--- a/mock/清洗后_活动运营数据.xlsx
+++ b/mock/清洗后_活动运营数据.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4658,13 +4658,29 @@
       </c>
     </row>
     <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>活动结束</t>
+        </is>
+      </c>
       <c r="AZ20" s="6" t="inlineStr">
         <is>
           <t>这是模型自己算出的一些衍生指标，不是最开始数据集里的</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>活动结束</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>∂</t>
@@ -4701,7 +4717,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4881,7 +4897,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -5061,7 +5077,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5241,7 +5257,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -5421,7 +5437,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>已发布进行中</t>
+          <t>活动结束</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">

--- a/mock/清洗后_活动运营数据.xlsx
+++ b/mock/清洗后_活动运营数据.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD32"/>
+  <dimension ref="A1:BD24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.6634615384615" customWidth="1" min="1" max="1"/>
@@ -4658,932 +4658,902 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACT20260116906569</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>26.1泰州无锡·新开户存款意向客群B</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>7393</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>活动结束</t>
         </is>
       </c>
-      <c r="AZ20" s="6" t="inlineStr">
-        <is>
-          <t>这是模型自己算出的一些衍生指标，不是最开始数据集里的</t>
-        </is>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>促资产提升</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>399927672</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.412185461493971</v>
+      </c>
+      <c r="L20" t="n">
+        <v>130.457587580259</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3996</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0292556501621653</v>
+      </c>
+      <c r="O20" t="n">
+        <v>107</v>
+      </c>
+      <c r="P20" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>11</v>
+      </c>
+      <c r="R20" t="n">
+        <v>259949370.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>207959496.32</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1903.15011018457</v>
+      </c>
+      <c r="U20" t="n">
+        <v>56.8889073790715</v>
+      </c>
+      <c r="V20" t="n">
+        <v>79985534.40000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>585.592795905966</v>
+      </c>
+      <c r="X20" t="n">
+        <v>152.592795905966</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19996383.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>68.505983497939</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3696</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2593</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>51</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3542</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2822</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2817</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>41</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>248</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>116852</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>15623</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>17819071.43</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7770398.97</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>20842497.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>11.44</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27">
-      <c r="H27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ACT20260116906570</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>26.1泰州无锡·新开户存款意向客群C</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>7393</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>活动结束</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>∂</t>
-        </is>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>促资产提升</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>399927672</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.412185461493971</v>
+      </c>
+      <c r="L21" t="n">
+        <v>130.457587580259</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3996</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0292556501621653</v>
+      </c>
+      <c r="O21" t="n">
+        <v>107</v>
+      </c>
+      <c r="P21" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>259949370.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>207959496.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1903.15011018457</v>
+      </c>
+      <c r="U21" t="n">
+        <v>56.8889073790715</v>
+      </c>
+      <c r="V21" t="n">
+        <v>79985534.40000001</v>
+      </c>
+      <c r="W21" t="n">
+        <v>585.592795905966</v>
+      </c>
+      <c r="X21" t="n">
+        <v>152.592795905966</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>19996383.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>68.505983497939</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3696</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2593</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>51</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3542</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2822</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2817</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>41</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>248</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>116852</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>15623</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>17819071.43</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7770398.97</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>20842497.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>11.44</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
+    <row r="22">
+      <c r="A22" s="8" t="n">
         <v>45807</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ACT20260116906569</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>26.1泰州无锡·新开户存款意向客群B</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>45819</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>7393</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACT20250605104812</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25年6月理财到期客户承接专项</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>45813</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>针对6月理财产品到期客户进行资金承接与续投引导</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>12800</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>活动结束</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>促资产提升</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>399927672</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.412185461493971</v>
-      </c>
-      <c r="L28" t="n">
-        <v>130.457587580259</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3996</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.0292556501621653</v>
-      </c>
-      <c r="O28" t="n">
-        <v>107</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="J22" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>37968.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2150.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5420</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="O22" t="n">
+        <v>860</v>
+      </c>
+      <c r="P22" t="n">
+        <v>780</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>64</v>
+      </c>
+      <c r="R22" t="n">
+        <v>158000000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>121000000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12343.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>980.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>296000000</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23125</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1680.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>9860</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1420</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4280</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>610</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2150</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>230</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3680</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>480</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>96</v>
       </c>
-      <c r="Q28" t="n">
-        <v>11</v>
-      </c>
-      <c r="R28" t="n">
-        <v>259949370.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>207959496.32</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1903.15011018457</v>
-      </c>
-      <c r="U28" t="n">
-        <v>56.8889073790715</v>
-      </c>
-      <c r="V28" t="n">
-        <v>79985534.40000001</v>
-      </c>
-      <c r="W28" t="n">
-        <v>585.592795905966</v>
-      </c>
-      <c r="X28" t="n">
-        <v>152.592795905966</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>19996383.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>68.505983497939</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3696</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>71</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2593</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>51</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>3542</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AK22" t="n">
+        <v>58</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>78</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8600</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>720</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8960</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1240</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>38600000</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ACT20250410104126</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25年Q2理财到期客户续投专项活动</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>45757</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>45787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>面向二季度理财到期客户推荐续投产品及组合配置方案</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>活动结束</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>促资产提升</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>352000000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>40930.23</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3120.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3980</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="O23" t="n">
+        <v>720</v>
+      </c>
+      <c r="P23" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>42</v>
+      </c>
+      <c r="R23" t="n">
+        <v>98000000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>76000000</v>
+      </c>
+      <c r="T23" t="n">
+        <v>11395.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>228000000</v>
+      </c>
+      <c r="W23" t="n">
+        <v>26511.63</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2280.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>210.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7240</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3160</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>520</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2840</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>420</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>86</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL23" t="n">
         <v>52</v>
       </c>
-      <c r="AG28" t="n">
-        <v>2822</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>57</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2817</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM28" t="n">
+      <c r="AM23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>81</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>12400</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6450</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>29800000</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>18600000</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACT20250520104605</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25年理财到期资金承接·高净值客户专班</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>45828</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>针对高净值客户理财到期资金提供专属承接与再配置方案</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>活动结束</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>促价值转化</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>428000000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>133750</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5680.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2380</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7438</v>
+      </c>
+      <c r="O24" t="n">
+        <v>320</v>
+      </c>
+      <c r="P24" t="n">
+        <v>290</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="T24" t="n">
+        <v>31875</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2160.8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>296000000</v>
+      </c>
+      <c r="W24" t="n">
+        <v>92500</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4320.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>480.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>380</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>260</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>86</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AR24" t="n">
         <v>7</v>
       </c>
-      <c r="AN28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>41</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1740</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>248</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>116852</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>15623</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>17819071.43</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7770398.97</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>20842497.4</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>45807</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ACT20260116906570</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>26.1泰州无锡·新开户存款意向客群C</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>45819</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>7393</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>活动结束</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>促资产提升</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>399927672</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.412185461493971</v>
-      </c>
-      <c r="L29" t="n">
-        <v>130.457587580259</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3996</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.0292556501621653</v>
-      </c>
-      <c r="O29" t="n">
-        <v>107</v>
-      </c>
-      <c r="P29" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>11</v>
-      </c>
-      <c r="R29" t="n">
-        <v>259949370.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>207959496.32</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1903.15011018457</v>
-      </c>
-      <c r="U29" t="n">
-        <v>56.8889073790715</v>
-      </c>
-      <c r="V29" t="n">
-        <v>79985534.40000001</v>
-      </c>
-      <c r="W29" t="n">
-        <v>585.592795905966</v>
-      </c>
-      <c r="X29" t="n">
-        <v>152.592795905966</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>19996383.6</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>68.505983497939</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3696</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>71</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2593</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>51</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>3542</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>52</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2822</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>57</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2817</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>41</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1740</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>248</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>116852</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>15623</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>17819071.43</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>7770398.97</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>20842497.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>45807</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ACT20250605104812</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>25年6月理财到期客户承接专项</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>45813</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>45838</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>针对6月理财产品到期客户进行资金承接与续投引导</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>12800</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>活动结束</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>促资产提升</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>486000000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>37968.75</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2150.4</v>
-      </c>
-      <c r="M30" t="n">
-        <v>5420</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.4234</v>
-      </c>
-      <c r="O30" t="n">
-        <v>860</v>
-      </c>
-      <c r="P30" t="n">
-        <v>780</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>64</v>
-      </c>
-      <c r="R30" t="n">
-        <v>158000000</v>
-      </c>
-      <c r="S30" t="n">
-        <v>121000000</v>
-      </c>
-      <c r="T30" t="n">
-        <v>12343.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>980.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>296000000</v>
-      </c>
-      <c r="W30" t="n">
-        <v>23125</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1680.2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>9860</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1420</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4280</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>610</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2150</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>230</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3680</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>480</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>96</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>58</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>72</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>78</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>8600</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>720</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8960</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1240</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>38600000</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>12400000</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>21500000</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>45807</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ACT20250410104126</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>25年Q2理财到期客户续投专项活动</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>45757</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>45787</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>面向二季度理财到期客户推荐续投产品及组合配置方案</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>8600</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>活动结束</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>促资产提升</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>352000000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>40930.23</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3120.8</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3980</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.4628</v>
-      </c>
-      <c r="O31" t="n">
-        <v>720</v>
-      </c>
-      <c r="P31" t="n">
-        <v>650</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>42</v>
-      </c>
-      <c r="R31" t="n">
-        <v>98000000</v>
-      </c>
-      <c r="S31" t="n">
-        <v>76000000</v>
-      </c>
-      <c r="T31" t="n">
-        <v>11395.35</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1240.6</v>
-      </c>
-      <c r="V31" t="n">
-        <v>228000000</v>
-      </c>
-      <c r="W31" t="n">
-        <v>26511.63</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2280.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>210.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>7240</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1180</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3160</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>520</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1580</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2840</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>420</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>86</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>68</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>52</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>81</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>12400</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1350</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>6450</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>980</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>29800000</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>18600000</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>12.35</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>45807</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ACT20250520104605</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>25年理财到期资金承接·高净值客户专班</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>45828</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>针对高净值客户理财到期资金提供专属承接与再配置方案</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="AS24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>28600</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW24" t="n">
         <v>3200</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>活动结束</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>促价值转化</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>428000000</v>
-      </c>
-      <c r="K32" t="n">
-        <v>133750</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5680.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2380</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.7438</v>
-      </c>
-      <c r="O32" t="n">
-        <v>320</v>
-      </c>
-      <c r="P32" t="n">
-        <v>290</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>18</v>
-      </c>
-      <c r="R32" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="S32" t="n">
-        <v>86000000</v>
-      </c>
-      <c r="T32" t="n">
-        <v>31875</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2160.8</v>
-      </c>
-      <c r="V32" t="n">
-        <v>296000000</v>
-      </c>
-      <c r="W32" t="n">
-        <v>92500</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4320.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>480.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2980</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1620</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>240</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1980</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>260</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>86</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>45</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>28600</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>3200</v>
-      </c>
-      <c r="AX32" t="n">
+      <c r="AX24" t="n">
         <v>2680</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY24" t="n">
         <v>360</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ24" t="n">
         <v>10</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA24" t="n">
         <v>24600000</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB24" t="n">
         <v>6900000</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC24" t="n">
         <v>15800000</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD24" t="n">
         <v>8.92</v>
       </c>
     </row>

--- a/mock/清洗后_活动运营数据.xlsx
+++ b/mock/清洗后_活动运营数据.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>26.1泰州无锡·新开户存款意向客群</t>
+          <t>26.1临川云泽·新开户存款意向客群</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.1泰州无锡·新开户存款意向客群B</t>
+          <t>26.1临川云泽·新开户存款意向客群B</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26.1泰州无锡·新开户存款意向客群C</t>
+          <t>26.1临川云泽·新开户存款意向客群C</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">

--- a/mock/清洗后_活动运营数据.xlsx
+++ b/mock/清洗后_活动运营数据.xlsx
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25年二季度非价值客群新拓专项</t>
+          <t>DEMO-25年二季度非价值客群新拓专项</t>
         </is>
       </c>
       <c r="D2" s="7" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>25年增金礼活动·仅二非价值新客</t>
+          <t>DEMO-25年增金礼活动·仅二非价值新客</t>
         </is>
       </c>
       <c r="D3" s="7" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>25年Q1非价值拓新专班（更新版）</t>
+          <t>DEMO-25年Q1非价值拓新专班（更新版）</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>25年T1流失召回输送·专班</t>
+          <t>DEMO-25年T1流失召回输送·专班</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>25年存量流失I类户首期（0512）</t>
+          <t>DEMO-25年存量流失I类户首期（0512）</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>LUM固化客群名单包</t>
+          <t>DEMO-LUM固化客群名单包</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>25年存量流失I类户二期（0512）</t>
+          <t>DEMO-25年存量流失I类户二期（0512）</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>LUM固化名单包（补发版）</t>
+          <t>DEMO-LUM固化名单包（补发版）</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>仅二专享·财气增金礼首期</t>
+          <t>DEMO-仅二专享·财气增金礼首期</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>25年5月优质仅二客群财气礼</t>
+          <t>DEMO-25年5月优质仅二客群财气礼</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>三月特邀·招财气双次触达活动</t>
+          <t>DEMO-三月特邀·招财气双次触达活动</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>三月招财气赢礼·特邀专场</t>
+          <t>DEMO-三月招财气赢礼·特邀专场</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>支付促活·AUM理财客群包2</t>
+          <t>DEMO-支付促活·AUM理财客群包2</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>支付固化名单2·支付促活场</t>
+          <t>DEMO-支付固化名单2·支付促活场</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>支付固化名单3·支付促活场</t>
+          <t>DEMO-支付固化名单3·支付促活场</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>25年Q1财气礼·32万客群包</t>
+          <t>DEMO-25年Q1财气礼·32万客群包</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>支付促活·AUM存款客群包1</t>
+          <t>DEMO-支付促活·AUM存款客群包1</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>26.1临川云泽·新开户存款意向客群</t>
+          <t>DEMO-26.1临川云泽·新开户存款意向客群</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.1临川云泽·新开户存款意向客群B</t>
+          <t>DEMO-26.1临川云泽·新开户存款意向客群B</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26.1临川云泽·新开户存款意向客群C</t>
+          <t>DEMO-26.1临川云泽·新开户存款意向客群C</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>25年6月理财到期客户承接专项</t>
+          <t>DEMO-25年6月理财到期客户承接专项</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>25年Q2理财到期客户续投专项活动</t>
+          <t>DEMO-25年Q2理财到期客户续投专项活动</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25年理财到期资金承接·高净值客户专班</t>
+          <t>DEMO-25年理财到期资金承接·高净值客户专班</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
